--- a/ref/Placa Base/PB_VERIFICACIONES.xlsx
+++ b/ref/Placa Base/PB_VERIFICACIONES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.10.0.30\Civil\03 - STD TEKLA\ref\Placa Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\03 - STD TEKLA\ref\Placa Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3A5AC3-AAA1-485D-8898-FBBFB263229A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993156C8-4DE6-49B3-B932-1C1CBC62283E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PB" sheetId="1" r:id="rId1"/>
@@ -295,7 +295,6 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -362,30 +361,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -407,6 +382,22 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -424,6 +415,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -871,22 +863,30 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFBFBFBF"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFBFBFBF"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -902,27 +902,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}" name="Table1" displayName="Table1" ref="A1:O30" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}" name="Table1" displayName="Table1" ref="A1:O30" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:O30" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{F50DDB28-7D44-48CC-B5E4-97688A435C4B}" name="Perfil" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{35C5EE2C-AEE7-4B69-9BF3-B2D0A827EA20}" name="Variante" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{9D59C8AF-EDEB-44CE-AC7B-393F6F67F352}" name="Etapa" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{2AB36A82-CB12-40DD-81A0-039A48826490}" name="Placa (mm)" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{A2C839AD-2B0A-402A-9B8E-08E4937E9FE4}" name="D anclaje" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{8C66F9C1-C32D-4CDD-867B-D238E01DFC92}" name="t placa (mm)" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{B41F9EB9-8820-4BF0-80A3-5CAF811BEE17}" name="h_ef (mm)" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{BFA1CBF2-CDCF-47DB-A0F5-B1641E80C69E}" name="Proy. sobre placa (mm)" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{55D39B72-64CD-4D9A-BBE5-EC0082C4FBE7}" name="s1 (mm) // d" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{231757F5-DDD4-45FE-8BA5-8AA9517A80A4}" name="s2 (mm) // bf" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{77E3C361-ACB2-41B6-9E69-00B7E3E82790}" name="s1 (mm) // redondeado" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{F50DDB28-7D44-48CC-B5E4-97688A435C4B}" name="Perfil" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{35C5EE2C-AEE7-4B69-9BF3-B2D0A827EA20}" name="Variante" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{9D59C8AF-EDEB-44CE-AC7B-393F6F67F352}" name="Etapa" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2AB36A82-CB12-40DD-81A0-039A48826490}" name="Placa (mm)" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{A2C839AD-2B0A-402A-9B8E-08E4937E9FE4}" name="D anclaje" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{8C66F9C1-C32D-4CDD-867B-D238E01DFC92}" name="t placa (mm)" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{B41F9EB9-8820-4BF0-80A3-5CAF811BEE17}" name="h_ef (mm)" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{BFA1CBF2-CDCF-47DB-A0F5-B1641E80C69E}" name="Proy. sobre placa (mm)" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{55D39B72-64CD-4D9A-BBE5-EC0082C4FBE7}" name="s1 (mm) // d" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{231757F5-DDD4-45FE-8BA5-8AA9517A80A4}" name="s2 (mm) // bf" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{77E3C361-ACB2-41B6-9E69-00B7E3E82790}" name="s1 (mm) // redondeado" dataDxfId="3">
       <calculatedColumnFormula>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{429B5AC0-DB41-4621-9EA4-3DA68D8031EB}" name="s2 (mm) // redondeado" dataDxfId="1">
+    <tableColumn id="17" xr3:uid="{429B5AC0-DB41-4621-9EA4-3DA68D8031EB}" name="s2 (mm) // redondeado" dataDxfId="2">
       <calculatedColumnFormula>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9F453753-33C9-42EB-840E-543FF93A5659}" name="Rigidizadores" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{9A662CA9-9573-4ACA-B72C-F671E53AB467}" name="Arand. 2° (mm)" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{9F453753-33C9-42EB-840E-543FF93A5659}" name="Rigidizadores" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{9A662CA9-9573-4ACA-B72C-F671E53AB467}" name="Arand. 2° (mm)" dataDxfId="0"/>
     <tableColumn id="15" xr3:uid="{39D81073-7FBD-4316-A1E0-D3CD09A671CC}" name="Preset">
       <calculatedColumnFormula>+_xlfn.CONCAT(A2,"-",IF(B2="ARTICULADA","ART","EMP"),"-",C2)</calculatedColumnFormula>
     </tableColumn>
@@ -1217,24 +1217,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="25.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="12" width="14.88671875" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1301,11 +1301,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G2" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B2="Articulada",12,18),-1)</f>
+        <f t="shared" ref="G2:G11" si="0">+ROUNDUP(3/4*25.4*IF(B2="Articulada",12,18),-1)</f>
         <v>230</v>
       </c>
       <c r="H2" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I2" s="2">
         <v>100</v>
@@ -1328,11 +1328,11 @@
         <v>18</v>
       </c>
       <c r="O2" t="str">
-        <f>+_xlfn.CONCAT(A2,"-",IF(B2="ARTICULADA","ART","EMP"),"-",C2)</f>
+        <f t="shared" ref="O2:O30" si="1">+_xlfn.CONCAT(A2,"-",IF(B2="ARTICULADA","ART","EMP"),"-",C2)</f>
         <v>W6x15-ART-1°</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1352,11 +1352,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G3" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B3="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="H3" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I3" s="2">
         <v>243</v>
@@ -1379,11 +1379,11 @@
         <v>18</v>
       </c>
       <c r="O3" t="str">
-        <f>+_xlfn.CONCAT(A3,"-",IF(B3="ARTICULADA","ART","EMP"),"-",C3)</f>
+        <f t="shared" si="1"/>
         <v>W6x15-EMP-1°</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1403,11 +1403,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G4" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B4="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="H4" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2">
         <v>293</v>
@@ -1430,11 +1430,11 @@
         <v>20</v>
       </c>
       <c r="O4" t="str">
-        <f>+_xlfn.CONCAT(A4,"-",IF(B4="ARTICULADA","ART","EMP"),"-",C4)</f>
+        <f t="shared" si="1"/>
         <v>W6x15-EMP-2°</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1454,11 +1454,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G5" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B5="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>230</v>
       </c>
-      <c r="H5" s="3">
-        <v>86</v>
+      <c r="H5" s="2">
+        <v>60</v>
       </c>
       <c r="I5" s="3">
         <v>150</v>
@@ -1481,11 +1481,11 @@
         <v>18</v>
       </c>
       <c r="O5" t="str">
-        <f>+_xlfn.CONCAT(A5,"-",IF(B5="ARTICULADA","ART","EMP"),"-",C5)</f>
+        <f t="shared" si="1"/>
         <v>W8x18-ART-1°</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
@@ -1505,11 +1505,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G6" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B6="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="H6" s="3">
-        <v>86</v>
+      <c r="H6" s="2">
+        <v>60</v>
       </c>
       <c r="I6" s="3">
         <v>293</v>
@@ -1532,11 +1532,11 @@
         <v>18</v>
       </c>
       <c r="O6" t="str">
-        <f>+_xlfn.CONCAT(A6,"-",IF(B6="ARTICULADA","ART","EMP"),"-",C6)</f>
+        <f t="shared" si="1"/>
         <v>W8x18-EMP-1°</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
@@ -1556,11 +1556,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G7" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B7="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="H7" s="3">
-        <v>86</v>
+      <c r="H7" s="2">
+        <v>60</v>
       </c>
       <c r="I7" s="3">
         <v>343</v>
@@ -1583,11 +1583,11 @@
         <v>20</v>
       </c>
       <c r="O7" t="str">
-        <f>+_xlfn.CONCAT(A7,"-",IF(B7="ARTICULADA","ART","EMP"),"-",C7)</f>
+        <f t="shared" si="1"/>
         <v>W8x18-EMP-2°</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1607,11 +1607,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G8" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B8="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>230</v>
       </c>
       <c r="H8" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I8" s="2">
         <v>150</v>
@@ -1634,11 +1634,11 @@
         <v>18</v>
       </c>
       <c r="O8" t="str">
-        <f>+_xlfn.CONCAT(A8,"-",IF(B8="ARTICULADA","ART","EMP"),"-",C8)</f>
+        <f t="shared" si="1"/>
         <v>W8x31-ART-1°</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -1658,11 +1658,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G9" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B9="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>230</v>
       </c>
       <c r="H9" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I9" s="2">
         <v>150</v>
@@ -1685,11 +1685,11 @@
         <v>20</v>
       </c>
       <c r="O9" t="str">
-        <f>+_xlfn.CONCAT(A9,"-",IF(B9="ARTICULADA","ART","EMP"),"-",C9)</f>
+        <f t="shared" si="1"/>
         <v>W8x31-ART-2°</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -1709,11 +1709,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G10" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B10="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="H10" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I10" s="2">
         <v>293</v>
@@ -1736,11 +1736,11 @@
         <v>18</v>
       </c>
       <c r="O10" t="str">
-        <f>+_xlfn.CONCAT(A10,"-",IF(B10="ARTICULADA","ART","EMP"),"-",C10)</f>
+        <f t="shared" si="1"/>
         <v>W8x31-EMP-1°</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -1760,11 +1760,11 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G11" s="2">
-        <f>+ROUNDUP(3/4*25.4*IF(B11="Articulada",12,18),-1)</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="H11" s="2">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I11" s="2">
         <v>343</v>
@@ -1787,11 +1787,11 @@
         <v>20</v>
       </c>
       <c r="O11" t="str">
-        <f>+_xlfn.CONCAT(A11,"-",IF(B11="ARTICULADA","ART","EMP"),"-",C11)</f>
+        <f t="shared" si="1"/>
         <v>W8x31-EMP-2°</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>25.4</v>
       </c>
       <c r="G12" s="2">
-        <f>+ROUNDUP(25.4*IF(B12="Articulada",12,18),-1)</f>
+        <f t="shared" ref="G12:G18" si="2">+ROUNDUP(25.4*IF(B12="Articulada",12,18),-1)</f>
         <v>310</v>
       </c>
       <c r="H12" s="3">
@@ -1838,11 +1838,11 @@
         <v>18</v>
       </c>
       <c r="O12" t="str">
-        <f>+_xlfn.CONCAT(A12,"-",IF(B12="ARTICULADA","ART","EMP"),"-",C12)</f>
+        <f t="shared" si="1"/>
         <v>W10x45-ART-1°</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>25.4</v>
       </c>
       <c r="G13" s="2">
-        <f>+ROUNDUP(25.4*IF(B13="Articulada",12,18),-1)</f>
+        <f t="shared" si="2"/>
         <v>460</v>
       </c>
       <c r="H13" s="3">
@@ -1889,11 +1889,11 @@
         <v>18</v>
       </c>
       <c r="O13" t="str">
-        <f>+_xlfn.CONCAT(A13,"-",IF(B13="ARTICULADA","ART","EMP"),"-",C13)</f>
+        <f t="shared" si="1"/>
         <v>W10x45-EMP-1°</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>25.4</v>
       </c>
       <c r="G14" s="2">
-        <f>+ROUNDUP(25.4*IF(B14="Articulada",12,18),-1)</f>
+        <f t="shared" si="2"/>
         <v>460</v>
       </c>
       <c r="H14" s="3">
@@ -1940,11 +1940,11 @@
         <v>31</v>
       </c>
       <c r="O14" t="str">
-        <f>+_xlfn.CONCAT(A14,"-",IF(B14="ARTICULADA","ART","EMP"),"-",C14)</f>
+        <f t="shared" si="1"/>
         <v>W10x45-EMP-2°</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>25.4</v>
       </c>
       <c r="G15" s="2">
-        <f>+ROUNDUP(25.4*IF(B15="Articulada",12,18),-1)</f>
+        <f t="shared" si="2"/>
         <v>310</v>
       </c>
       <c r="H15" s="2">
@@ -1991,11 +1991,11 @@
         <v>18</v>
       </c>
       <c r="O15" t="str">
-        <f>+_xlfn.CONCAT(A15,"-",IF(B15="ARTICULADA","ART","EMP"),"-",C15)</f>
+        <f t="shared" si="1"/>
         <v>W12x50-ART-1°</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>25.4</v>
       </c>
       <c r="G16" s="2">
-        <f>+ROUNDUP(25.4*IF(B16="Articulada",12,18),-1)</f>
+        <f t="shared" si="2"/>
         <v>460</v>
       </c>
       <c r="H16" s="2">
@@ -2042,11 +2042,11 @@
         <v>18</v>
       </c>
       <c r="O16" t="str">
-        <f>+_xlfn.CONCAT(A16,"-",IF(B16="ARTICULADA","ART","EMP"),"-",C16)</f>
+        <f t="shared" si="1"/>
         <v>W12x50-EMP-1°</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>25.4</v>
       </c>
       <c r="G17" s="2">
-        <f>+ROUNDUP(25.4*IF(B17="Articulada",12,18),-1)</f>
+        <f t="shared" si="2"/>
         <v>310</v>
       </c>
       <c r="H17" s="3">
@@ -2093,11 +2093,11 @@
         <v>18</v>
       </c>
       <c r="O17" t="str">
-        <f>+_xlfn.CONCAT(A17,"-",IF(B17="ARTICULADA","ART","EMP"),"-",C17)</f>
+        <f t="shared" si="1"/>
         <v>W14x74-ART-1°</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>25.4</v>
       </c>
       <c r="G18" s="2">
-        <f>+ROUNDUP(25.4*IF(B18="Articulada",12,18),-1)</f>
+        <f t="shared" si="2"/>
         <v>460</v>
       </c>
       <c r="H18" s="3">
@@ -2144,11 +2144,11 @@
         <v>18</v>
       </c>
       <c r="O18" t="str">
-        <f>+_xlfn.CONCAT(A18,"-",IF(B18="ARTICULADA","ART","EMP"),"-",C18)</f>
+        <f t="shared" si="1"/>
         <v>W14x74-EMP-1°</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
@@ -2195,11 +2195,11 @@
         <v>18</v>
       </c>
       <c r="O19" t="str">
-        <f>+_xlfn.CONCAT(A19,"-",IF(B19="ARTICULADA","ART","EMP"),"-",C19)</f>
+        <f t="shared" si="1"/>
         <v>HEB160-ART-1°</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
@@ -2246,11 +2246,11 @@
         <v>18</v>
       </c>
       <c r="O20" t="str">
-        <f>+_xlfn.CONCAT(A20,"-",IF(B20="ARTICULADA","ART","EMP"),"-",C20)</f>
+        <f t="shared" si="1"/>
         <v>HEB160-EMP-1°</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
@@ -2297,11 +2297,11 @@
         <v>20</v>
       </c>
       <c r="O21" t="str">
-        <f>+_xlfn.CONCAT(A21,"-",IF(B21="ARTICULADA","ART","EMP"),"-",C21)</f>
+        <f t="shared" si="1"/>
         <v>HEB160-EMP-2°</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>36</v>
       </c>
@@ -2348,11 +2348,11 @@
         <v>18</v>
       </c>
       <c r="O22" t="str">
-        <f>+_xlfn.CONCAT(A22,"-",IF(B22="ARTICULADA","ART","EMP"),"-",C22)</f>
+        <f t="shared" si="1"/>
         <v>HEB200-ART-1°</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>36</v>
       </c>
@@ -2399,11 +2399,11 @@
         <v>18</v>
       </c>
       <c r="O23" t="str">
-        <f>+_xlfn.CONCAT(A23,"-",IF(B23="ARTICULADA","ART","EMP"),"-",C23)</f>
+        <f t="shared" si="1"/>
         <v>HEB200-EMP-1°</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>36</v>
       </c>
@@ -2450,11 +2450,11 @@
         <v>31</v>
       </c>
       <c r="O24" t="str">
-        <f>+_xlfn.CONCAT(A24,"-",IF(B24="ARTICULADA","ART","EMP"),"-",C24)</f>
+        <f t="shared" si="1"/>
         <v>HEB200-EMP-2°</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>45</v>
       </c>
@@ -2501,11 +2501,11 @@
         <v>18</v>
       </c>
       <c r="O25" t="str">
-        <f>+_xlfn.CONCAT(A25,"-",IF(B25="ARTICULADA","ART","EMP"),"-",C25)</f>
+        <f t="shared" si="1"/>
         <v>UPN140C-EMP-1°</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>45</v>
       </c>
@@ -2552,11 +2552,11 @@
         <v>20</v>
       </c>
       <c r="O26" t="str">
-        <f>+_xlfn.CONCAT(A26,"-",IF(B26="ARTICULADA","ART","EMP"),"-",C26)</f>
+        <f t="shared" si="1"/>
         <v>UPN140C-EMP-2°</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>46</v>
       </c>
@@ -2603,11 +2603,11 @@
         <v>18</v>
       </c>
       <c r="O27" t="str">
-        <f>+_xlfn.CONCAT(A27,"-",IF(B27="ARTICULADA","ART","EMP"),"-",C27)</f>
+        <f t="shared" si="1"/>
         <v>UPN180C-EMP-1°</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>46</v>
       </c>
@@ -2654,11 +2654,11 @@
         <v>20</v>
       </c>
       <c r="O28" t="str">
-        <f>+_xlfn.CONCAT(A28,"-",IF(B28="ARTICULADA","ART","EMP"),"-",C28)</f>
+        <f t="shared" si="1"/>
         <v>UPN180C-EMP-2°</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>47</v>
       </c>
@@ -2705,11 +2705,11 @@
         <v>18</v>
       </c>
       <c r="O29" t="str">
-        <f>+_xlfn.CONCAT(A29,"-",IF(B29="ARTICULADA","ART","EMP"),"-",C29)</f>
+        <f t="shared" si="1"/>
         <v>UPN220C-EMP-1°</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>47</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>31</v>
       </c>
       <c r="O30" t="str">
-        <f>+_xlfn.CONCAT(A30,"-",IF(B30="ARTICULADA","ART","EMP"),"-",C30)</f>
+        <f t="shared" si="1"/>
         <v>UPN220C-EMP-2°</v>
       </c>
     </row>

--- a/ref/Placa Base/PB_VERIFICACIONES.xlsx
+++ b/ref/Placa Base/PB_VERIFICACIONES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\03 - STD TEKLA\ref\Placa Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.10.0.30\Civil\03 - STD TEKLA\ref\Placa Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993156C8-4DE6-49B3-B932-1C1CBC62283E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E4A255-53C3-494C-AA92-16D4356F0357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PB" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="50">
   <si>
     <t>Perfil</t>
   </si>
@@ -65,9 +65,6 @@
     <t>s2 (mm) // bf</t>
   </si>
   <si>
-    <t>Rigidizadores</t>
-  </si>
-  <si>
     <t>Arand. 2° (mm)</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>350x350</t>
   </si>
   <si>
-    <t>Sí</t>
-  </si>
-  <si>
     <t>W8x18</t>
   </si>
   <si>
@@ -177,6 +171,18 @@
   </si>
   <si>
     <t>UPN220C</t>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <t>Rigidizadores (va componente esp)</t>
+  </si>
+  <si>
+    <t>350x280</t>
+  </si>
+  <si>
+    <t>400x350</t>
   </si>
 </sst>
 </file>
@@ -209,7 +215,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,8 +238,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -256,11 +274,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -274,11 +318,63 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -902,30 +998,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}" name="Table1" displayName="Table1" ref="A1:O30" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:O30" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{F50DDB28-7D44-48CC-B5E4-97688A435C4B}" name="Perfil" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{35C5EE2C-AEE7-4B69-9BF3-B2D0A827EA20}" name="Variante" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{9D59C8AF-EDEB-44CE-AC7B-393F6F67F352}" name="Etapa" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{2AB36A82-CB12-40DD-81A0-039A48826490}" name="Placa (mm)" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{A2C839AD-2B0A-402A-9B8E-08E4937E9FE4}" name="D anclaje" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{8C66F9C1-C32D-4CDD-867B-D238E01DFC92}" name="t placa (mm)" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{B41F9EB9-8820-4BF0-80A3-5CAF811BEE17}" name="h_ef (mm)" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{BFA1CBF2-CDCF-47DB-A0F5-B1641E80C69E}" name="Proy. sobre placa (mm)" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{55D39B72-64CD-4D9A-BBE5-EC0082C4FBE7}" name="s1 (mm) // d" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{231757F5-DDD4-45FE-8BA5-8AA9517A80A4}" name="s2 (mm) // bf" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{77E3C361-ACB2-41B6-9E69-00B7E3E82790}" name="s1 (mm) // redondeado" dataDxfId="3">
-      <calculatedColumnFormula>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{429B5AC0-DB41-4621-9EA4-3DA68D8031EB}" name="s2 (mm) // redondeado" dataDxfId="2">
-      <calculatedColumnFormula>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" xr3:uid="{9F453753-33C9-42EB-840E-543FF93A5659}" name="Rigidizadores" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{9A662CA9-9573-4ACA-B72C-F671E53AB467}" name="Arand. 2° (mm)" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}" name="Table1" displayName="Table1" ref="A1:P30" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:P30" xr:uid="{E8367052-7810-4CA1-9C70-F48FA2998CC0}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{F50DDB28-7D44-48CC-B5E4-97688A435C4B}" name="Perfil" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{35C5EE2C-AEE7-4B69-9BF3-B2D0A827EA20}" name="Variante" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{9D59C8AF-EDEB-44CE-AC7B-393F6F67F352}" name="Etapa" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{2AB36A82-CB12-40DD-81A0-039A48826490}" name="Placa (mm)" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{A2C839AD-2B0A-402A-9B8E-08E4937E9FE4}" name="D anclaje" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{8C66F9C1-C32D-4CDD-867B-D238E01DFC92}" name="t placa (mm)" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{B41F9EB9-8820-4BF0-80A3-5CAF811BEE17}" name="h_ef (mm)" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{BFA1CBF2-CDCF-47DB-A0F5-B1641E80C69E}" name="Proy. sobre placa (mm)" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{55D39B72-64CD-4D9A-BBE5-EC0082C4FBE7}" name="s1 (mm) // d" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{231757F5-DDD4-45FE-8BA5-8AA9517A80A4}" name="s2 (mm) // bf" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{77E3C361-ACB2-41B6-9E69-00B7E3E82790}" name="s1 (mm) // redondeado" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{429B5AC0-DB41-4621-9EA4-3DA68D8031EB}" name="s2 (mm) // redondeado" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{9F453753-33C9-42EB-840E-543FF93A5659}" name="Rigidizadores (va componente esp)" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{9A662CA9-9573-4ACA-B72C-F671E53AB467}" name="Arand. 2° (mm)" dataDxfId="1"/>
     <tableColumn id="15" xr3:uid="{39D81073-7FBD-4316-A1E0-D3CD09A671CC}" name="Preset">
       <calculatedColumnFormula>+_xlfn.CONCAT(A2,"-",IF(B2="ARTICULADA","ART","EMP"),"-",C2)</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="11" xr3:uid="{98344727-E73D-4488-A582-40F4F1DFA3D3}" name="CHECK" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1216,25 +1309,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="25.44140625" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="12" width="14.88671875" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" customWidth="1"/>
-    <col min="14" max="14" width="17.44140625" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,36 +1359,39 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F2" s="2">
         <v>19.100000000000001</v>
@@ -1314,39 +1410,40 @@
         <v>90</v>
       </c>
       <c r="K2" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L2" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>90</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O2" t="str">
         <f t="shared" ref="O2:O30" si="1">+_xlfn.CONCAT(A2,"-",IF(B2="ARTICULADA","ART","EMP"),"-",C2)</f>
         <v>W6x15-ART-1°</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2">
         <v>19.100000000000001</v>
@@ -1365,39 +1462,40 @@
         <v>243</v>
       </c>
       <c r="K3" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="L3" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" si="1"/>
         <v>W6x15-EMP-1°</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2">
         <v>19.100000000000001</v>
@@ -1416,39 +1514,40 @@
         <v>293</v>
       </c>
       <c r="K4" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="L4" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="1"/>
         <v>W6x15-EMP-2°</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3">
         <v>19.100000000000001</v>
@@ -1467,39 +1566,40 @@
         <v>80</v>
       </c>
       <c r="K5" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L5" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>80</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" si="1"/>
         <v>W8x18-ART-1°</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3">
         <v>19.100000000000001</v>
@@ -1518,39 +1618,40 @@
         <v>293</v>
       </c>
       <c r="K6" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
+        <v>290</v>
+      </c>
+      <c r="L6" s="2">
         <v>300</v>
       </c>
-      <c r="L6" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
-        <v>300</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>24</v>
+      <c r="M6" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" si="1"/>
         <v>W8x18-EMP-1°</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3">
         <v>19.100000000000001</v>
@@ -1569,39 +1670,40 @@
         <v>343</v>
       </c>
       <c r="K7" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>350</v>
       </c>
       <c r="L7" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>350</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>24</v>
+      <c r="M7" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" si="1"/>
         <v>W8x18-EMP-2°</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2">
         <v>19.100000000000001</v>
@@ -1620,39 +1722,38 @@
         <v>150</v>
       </c>
       <c r="K8" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>150</v>
       </c>
       <c r="L8" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>150</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" si="1"/>
         <v>W8x31-ART-1°</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2">
         <v>19.100000000000001</v>
@@ -1671,39 +1772,38 @@
         <v>150</v>
       </c>
       <c r="K9" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>150</v>
       </c>
       <c r="L9" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>150</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" si="1"/>
         <v>W8x31-ART-2°</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2">
         <v>19.100000000000001</v>
@@ -1722,39 +1822,38 @@
         <v>293</v>
       </c>
       <c r="K10" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>300</v>
       </c>
       <c r="L10" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>300</v>
       </c>
       <c r="M10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O10" t="str">
         <f t="shared" si="1"/>
         <v>W8x31-EMP-1°</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="2">
         <v>19.100000000000001</v>
@@ -1773,39 +1872,38 @@
         <v>343</v>
       </c>
       <c r="K11" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>350</v>
       </c>
       <c r="L11" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>350</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="1"/>
         <v>W8x31-EMP-2°</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F12" s="3">
         <v>25.4</v>
@@ -1824,39 +1922,38 @@
         <v>150</v>
       </c>
       <c r="K12" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>200</v>
       </c>
       <c r="L12" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>150</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="1"/>
         <v>W10x45-ART-1°</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F13" s="3">
         <v>25.4</v>
@@ -1875,39 +1972,38 @@
         <v>324</v>
       </c>
       <c r="K13" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>330</v>
       </c>
       <c r="L13" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>330</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>24</v>
+      <c r="M13" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" si="1"/>
         <v>W10x45-EMP-1°</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3">
         <v>25.4</v>
@@ -1926,39 +2022,38 @@
         <v>374</v>
       </c>
       <c r="K14" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>380</v>
       </c>
       <c r="L14" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>380</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>24</v>
+      <c r="M14" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O14" t="str">
         <f t="shared" si="1"/>
         <v>W10x45-EMP-2°</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F15" s="2">
         <v>25.4</v>
@@ -1977,39 +2072,38 @@
         <v>150</v>
       </c>
       <c r="K15" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>250</v>
       </c>
       <c r="L15" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>150</v>
       </c>
       <c r="M15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" si="1"/>
         <v>W12x50-ART-1°</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F16" s="2">
         <v>25.4</v>
@@ -2028,39 +2122,38 @@
         <v>374</v>
       </c>
       <c r="K16" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>380</v>
       </c>
       <c r="L16" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>380</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="1"/>
         <v>W12x50-EMP-1°</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3">
         <v>25.4</v>
@@ -2079,39 +2172,38 @@
         <v>200</v>
       </c>
       <c r="K17" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>280</v>
       </c>
       <c r="L17" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>200</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="M17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="1"/>
         <v>W14x74-ART-1°</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
         <v>25.4</v>
@@ -2130,39 +2222,38 @@
         <v>374</v>
       </c>
       <c r="K18" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>360</v>
       </c>
       <c r="L18" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>380</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>24</v>
+      <c r="M18" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" si="1"/>
         <v>W14x74-EMP-1°</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F19" s="2">
         <v>19.100000000000001</v>
@@ -2181,39 +2272,38 @@
         <v>100</v>
       </c>
       <c r="K19" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>100</v>
       </c>
       <c r="L19" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>100</v>
       </c>
       <c r="M19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O19" t="str">
         <f t="shared" si="1"/>
         <v>HEB160-ART-1°</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2">
         <v>19.100000000000001</v>
@@ -2232,39 +2322,38 @@
         <v>243</v>
       </c>
       <c r="K20" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>250</v>
       </c>
       <c r="L20" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>250</v>
       </c>
       <c r="M20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O20" t="str">
         <f t="shared" si="1"/>
         <v>HEB160-EMP-1°</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20" s="5"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="2">
         <v>19.100000000000001</v>
@@ -2283,39 +2372,38 @@
         <v>293</v>
       </c>
       <c r="K21" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>300</v>
       </c>
       <c r="L21" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>300</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" si="1"/>
         <v>HEB160-EMP-2°</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21" s="5"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3">
         <v>25.4</v>
@@ -2334,39 +2422,38 @@
         <v>150</v>
       </c>
       <c r="K22" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>150</v>
       </c>
       <c r="L22" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>150</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="O22" t="str">
         <f t="shared" si="1"/>
         <v>HEB200-ART-1°</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P22" s="5"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3">
         <v>25.4</v>
@@ -2385,39 +2472,38 @@
         <v>324</v>
       </c>
       <c r="K23" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>330</v>
       </c>
       <c r="L23" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>330</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>24</v>
+      <c r="M23" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" si="1"/>
         <v>HEB200-EMP-1°</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P23" s="5"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3">
         <v>25.4</v>
@@ -2436,39 +2522,38 @@
         <v>374</v>
       </c>
       <c r="K24" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>380</v>
       </c>
       <c r="L24" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>380</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>24</v>
+      <c r="M24" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" si="1"/>
         <v>HEB200-EMP-2°</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24" s="5"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" s="2">
         <v>19.100000000000001</v>
@@ -2487,39 +2572,38 @@
         <v>143</v>
       </c>
       <c r="K25" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>200</v>
       </c>
       <c r="L25" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>150</v>
       </c>
       <c r="M25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N25" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" si="1"/>
         <v>UPN140C-EMP-1°</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P25" s="5"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" s="2">
         <v>19.100000000000001</v>
@@ -2538,39 +2622,38 @@
         <v>193</v>
       </c>
       <c r="K26" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>250</v>
       </c>
       <c r="L26" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>200</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" si="1"/>
         <v>UPN140C-EMP-2°</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P26" s="5"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3">
         <v>19.100000000000001</v>
@@ -2589,39 +2672,38 @@
         <v>193</v>
       </c>
       <c r="K27" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>250</v>
       </c>
       <c r="L27" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>200</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="M27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N27" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" si="1"/>
         <v>UPN180C-EMP-1°</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3">
         <v>19.100000000000001</v>
@@ -2640,39 +2722,38 @@
         <v>243</v>
       </c>
       <c r="K28" s="3">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>300</v>
       </c>
       <c r="L28" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>250</v>
       </c>
-      <c r="M28" s="3" t="s">
-        <v>24</v>
+      <c r="M28" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" si="1"/>
         <v>UPN180C-EMP-2°</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P28" s="5"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F29" s="2">
         <v>25.4</v>
@@ -2691,39 +2772,38 @@
         <v>224</v>
       </c>
       <c r="K29" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>330</v>
       </c>
       <c r="L29" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>230</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" si="1"/>
         <v>UPN220C-EMP-1°</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P29" s="5"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2">
         <v>25.4</v>
@@ -2742,23 +2822,22 @@
         <v>274</v>
       </c>
       <c r="K30" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s1 (mm) // d]],-1)</f>
         <v>380</v>
       </c>
       <c r="L30" s="2">
-        <f>+ROUNDUP(Table1[[#This Row],[s2 (mm) // bf]],-1)</f>
         <v>280</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O30" t="str">
         <f t="shared" si="1"/>
         <v>UPN220C-EMP-2°</v>
       </c>
+      <c r="P30" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ref/Placa Base/PB_VERIFICACIONES.xlsx
+++ b/ref/Placa Base/PB_VERIFICACIONES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.10.0.30\Civil\03 - STD TEKLA\ref\Placa Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E4A255-53C3-494C-AA92-16D4356F0357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D5DE00-D63E-450A-82E6-E4A747962B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PB" sheetId="1" r:id="rId1"/>
@@ -1722,10 +1722,10 @@
         <v>150</v>
       </c>
       <c r="K8" s="2">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="L8" s="2">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>16</v>
@@ -1737,7 +1737,9 @@
         <f t="shared" si="1"/>
         <v>W8x31-ART-1°</v>
       </c>
-      <c r="P8" s="5"/>
+      <c r="P8" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1772,10 +1774,10 @@
         <v>150</v>
       </c>
       <c r="K9" s="2">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="L9" s="2">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>16</v>
@@ -1787,7 +1789,9 @@
         <f t="shared" si="1"/>
         <v>W8x31-ART-2°</v>
       </c>
-      <c r="P9" s="5"/>
+      <c r="P9" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -1822,10 +1826,10 @@
         <v>293</v>
       </c>
       <c r="K10" s="2">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="L10" s="2">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>16</v>
@@ -1837,7 +1841,9 @@
         <f t="shared" si="1"/>
         <v>W8x31-EMP-1°</v>
       </c>
-      <c r="P10" s="5"/>
+      <c r="P10" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -1872,10 +1878,10 @@
         <v>343</v>
       </c>
       <c r="K11" s="2">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="L11" s="2">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>16</v>
@@ -1887,7 +1893,9 @@
         <f t="shared" si="1"/>
         <v>W8x31-EMP-2°</v>
       </c>
-      <c r="P11" s="5"/>
+      <c r="P11" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -1913,7 +1921,7 @@
         <v>310</v>
       </c>
       <c r="H12" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I12" s="3">
         <v>200</v>
@@ -1922,7 +1930,7 @@
         <v>150</v>
       </c>
       <c r="K12" s="3">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L12" s="2">
         <v>150</v>
@@ -1937,7 +1945,9 @@
         <f t="shared" si="1"/>
         <v>W10x45-ART-1°</v>
       </c>
-      <c r="P12" s="5"/>
+      <c r="P12" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -1963,7 +1973,7 @@
         <v>460</v>
       </c>
       <c r="H13" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I13" s="3">
         <v>324</v>
@@ -1972,10 +1982,10 @@
         <v>324</v>
       </c>
       <c r="K13" s="3">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="L13" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>16</v>
@@ -1987,7 +1997,9 @@
         <f t="shared" si="1"/>
         <v>W10x45-EMP-1°</v>
       </c>
-      <c r="P13" s="5"/>
+      <c r="P13" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
@@ -2013,7 +2025,7 @@
         <v>460</v>
       </c>
       <c r="H14" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3">
         <v>374</v>
@@ -2022,10 +2034,10 @@
         <v>374</v>
       </c>
       <c r="K14" s="3">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="L14" s="2">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>16</v>
@@ -2037,7 +2049,9 @@
         <f t="shared" si="1"/>
         <v>W10x45-EMP-2°</v>
       </c>
-      <c r="P14" s="5"/>
+      <c r="P14" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -2063,7 +2077,7 @@
         <v>310</v>
       </c>
       <c r="H15" s="2">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I15" s="2">
         <v>250</v>
@@ -2113,7 +2127,7 @@
         <v>460</v>
       </c>
       <c r="H16" s="2">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I16" s="2">
         <v>374</v>
@@ -2163,7 +2177,7 @@
         <v>310</v>
       </c>
       <c r="H17" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I17" s="3">
         <v>280</v>
@@ -2213,7 +2227,7 @@
         <v>460</v>
       </c>
       <c r="H18" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I18" s="3">
         <v>360</v>
@@ -2413,7 +2427,7 @@
         <v>310</v>
       </c>
       <c r="H22" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I22" s="3">
         <v>150</v>
@@ -2463,7 +2477,7 @@
         <v>460</v>
       </c>
       <c r="H23" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I23" s="3">
         <v>324</v>
@@ -2513,7 +2527,7 @@
         <v>460</v>
       </c>
       <c r="H24" s="3">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I24" s="3">
         <v>374</v>
@@ -2762,8 +2776,8 @@
         <f>+ROUNDUP(25.4*IF(B29="Articulada",12,18),-1)</f>
         <v>460</v>
       </c>
-      <c r="H29" s="2">
-        <v>114</v>
+      <c r="H29" s="3">
+        <v>90</v>
       </c>
       <c r="I29" s="2">
         <v>324</v>
@@ -2812,8 +2826,8 @@
         <f>+ROUNDUP(25.4*IF(B30="Articulada",12,18),-1)</f>
         <v>460</v>
       </c>
-      <c r="H30" s="2">
-        <v>114</v>
+      <c r="H30" s="3">
+        <v>90</v>
       </c>
       <c r="I30" s="2">
         <v>374</v>
